--- a/data/ecs.xlsx
+++ b/data/ecs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/UST914/Desktop/blg-475-project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9CE5DA-3289-904B-9F35-F3A679545A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAA1E87-8DEF-E84F-9B42-75115B9172B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="21000" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="443">
   <si>
     <t>Type</t>
   </si>
@@ -2834,6 +2834,21 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>- Total equivalence classes: 296</t>
+  </si>
+  <si>
+    <t>- Covered by base tests: 109 / 296 = 36.82%</t>
+  </si>
+  <si>
+    <t>- Covered by mutated tests: 241 / 296 = 81.42%</t>
+  </si>
+  <si>
+    <t>- Improvement: +132 ECs = +44.60 percentage points</t>
+  </si>
+  <si>
+    <t>- Still uncovered after mutation: 55 / 296 = 18.58%</t>
   </si>
 </sst>
 </file>
@@ -2843,7 +2858,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2875,13 +2890,6 @@
       <color theme="1"/>
       <name val="Menlo"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4187,10 +4195,13 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA593DA-B4E3-4349-9AE3-137E67A4A1FB}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>358</v>
       </c>
@@ -4203,8 +4214,11 @@
       <c r="D1" s="6" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="F1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>361</v>
       </c>
@@ -4217,8 +4231,11 @@
       <c r="D2" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>362</v>
       </c>
@@ -4231,8 +4248,11 @@
       <c r="D3" s="7">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>363</v>
       </c>
@@ -4245,8 +4265,11 @@
       <c r="D4" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>364</v>
       </c>
@@ -4259,8 +4282,11 @@
       <c r="D5" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>365</v>
       </c>
@@ -4274,7 +4300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>366</v>
       </c>
@@ -4288,7 +4314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>367</v>
       </c>
@@ -4302,7 +4328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>368</v>
       </c>
@@ -4316,7 +4342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>369</v>
       </c>
@@ -4330,7 +4356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>370</v>
       </c>
@@ -4344,7 +4370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>371</v>
       </c>
@@ -4358,7 +4384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>372</v>
       </c>
@@ -4372,7 +4398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>373</v>
       </c>
@@ -4386,7 +4412,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>374</v>
       </c>
@@ -4400,7 +4426,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>375</v>
       </c>

--- a/data/ecs.xlsx
+++ b/data/ecs.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/UST914/Desktop/blg-475-project/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\posti\Desktop\blg-475-project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAA1E87-8DEF-E84F-9B42-75115B9172B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C9D9CA-E38D-4C0D-B84B-3ABC04F752FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="21000" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Java0" sheetId="1" r:id="rId1"/>
-    <sheet name="Java1" sheetId="2" r:id="rId2"/>
-    <sheet name="Java5" sheetId="3" r:id="rId3"/>
-    <sheet name="Java8" sheetId="4" r:id="rId4"/>
-    <sheet name="Java13" sheetId="5" r:id="rId5"/>
-    <sheet name="Java16" sheetId="6" r:id="rId6"/>
-    <sheet name="Java18" sheetId="7" r:id="rId7"/>
-    <sheet name="Java20" sheetId="8" r:id="rId8"/>
-    <sheet name="Java25" sheetId="9" r:id="rId9"/>
-    <sheet name="Java29" sheetId="10" r:id="rId10"/>
-    <sheet name="Java32" sheetId="11" r:id="rId11"/>
-    <sheet name="Java40" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet1" sheetId="31" r:id="rId13"/>
+    <sheet name="results" sheetId="31" r:id="rId1"/>
+    <sheet name="Java0" sheetId="1" r:id="rId2"/>
+    <sheet name="Java1" sheetId="2" r:id="rId3"/>
+    <sheet name="Java5" sheetId="3" r:id="rId4"/>
+    <sheet name="Java8" sheetId="4" r:id="rId5"/>
+    <sheet name="Java13" sheetId="5" r:id="rId6"/>
+    <sheet name="Java16" sheetId="6" r:id="rId7"/>
+    <sheet name="Java18" sheetId="7" r:id="rId8"/>
+    <sheet name="Java20" sheetId="8" r:id="rId9"/>
+    <sheet name="Java25" sheetId="9" r:id="rId10"/>
+    <sheet name="Java29" sheetId="10" r:id="rId11"/>
+    <sheet name="Java32" sheetId="11" r:id="rId12"/>
+    <sheet name="Java40" sheetId="12" r:id="rId13"/>
     <sheet name="Java44" sheetId="13" r:id="rId14"/>
     <sheet name="Java46" sheetId="14" r:id="rId15"/>
     <sheet name="Java48" sheetId="15" r:id="rId16"/>
@@ -54,16 +54,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="537">
   <si>
     <t>Type</t>
   </si>
@@ -2849,6 +2850,288 @@
   </si>
   <si>
     <t>- Still uncovered after mutation: 55 / 296 = 18.58%</t>
+  </si>
+  <si>
+    <t>Covered by MutationDatasetTest?</t>
+  </si>
+  <si>
+    <t>Total suites</t>
+  </si>
+  <si>
+    <t>Passed suites</t>
+  </si>
+  <si>
+    <t>Failed suites</t>
+  </si>
+  <si>
+    <t>Total tests</t>
+  </si>
+  <si>
+    <t>Passed tests</t>
+  </si>
+  <si>
+    <t>Failed tests</t>
+  </si>
+  <si>
+    <t>Errors</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Suite</t>
+  </si>
+  <si>
+    <t>Tests</t>
+  </si>
+  <si>
+    <t>Failures</t>
+  </si>
+  <si>
+    <t>Time (s)</t>
+  </si>
+  <si>
+    <t>Failure summary</t>
+  </si>
+  <si>
+    <t>gpt54.task1.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>runsDatasetMutationChecks: Multiple Failures (1 failure) org.opentest4j.AssertionFailedError: Expected java.lang.Throwable to be thrown, but nothing was thrown.</t>
+  </si>
+  <si>
+    <t>gpt54.task129.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>runsDatasetMutationChecks: Multiple Failures (4 failures) org.opentest4j.AssertionFailedError: Expected java.lang.Throwable to be thrown, but nothing was thrown. org.opentest4j.AssertionFailedError: Expected java.lang.Throwable to be thrown, but n</t>
+  </si>
+  <si>
+    <t>gpt54.task13.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task156.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>runsDatasetMutationChecks: Multiple Failures (2 failures) org.opentest4j.AssertionFailedError: Expected java.lang.Throwable to be thrown, but nothing was thrown. org.opentest4j.AssertionFailedError: Expected java.lang.Throwable to be thrown, but n</t>
+  </si>
+  <si>
+    <t>gpt54.task160.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>runsDatasetMutationChecks: Multiple Failures (2 failures) org.opentest4j.AssertionFailedError: expected: &lt;64&gt; but was: &lt;512&gt; org.opentest4j.AssertionFailedError: Expected java.lang.Throwable to be thrown, but nothing was thrown.</t>
+  </si>
+  <si>
+    <t>gpt54.task32.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task44.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task46.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task55.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>gpt54.task0.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>gpt54.task0.SolutionTest</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>gpt54.task1.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task109.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task109.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task110.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task110.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task124.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task124.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task129.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task13.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task140.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task140.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task141.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task141.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task156.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task16.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task16.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task160.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task162.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task162.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task18.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task18.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task20.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task20.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task25.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task25.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task29.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task29.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task32.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task40.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task40.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task44.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task46.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task48.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task48.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task5.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task5.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task55.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task57.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task57.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task58.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task58.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task65.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task65.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task69.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task69.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task76.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task76.SolutionTest</t>
+  </si>
+  <si>
+    <t>gpt54.task8.MutationDatasetTest</t>
+  </si>
+  <si>
+    <t>gpt54.task8.SolutionTest</t>
+  </si>
+  <si>
+    <t>Full Test Run (gpt54 only)</t>
+  </si>
+  <si>
+    <t>Failed cases</t>
+  </si>
+  <si>
+    <t>Failed case(s)</t>
+  </si>
+  <si>
+    <t>line 34: assertThrows on s.separateParenGroups("(()")</t>
+  </si>
+  <si>
+    <t>line 23: non-square grid; line 24: N &lt; 2; line 25: k = 0; line 26: repeated values grid</t>
+  </si>
+  <si>
+    <t>line 28: assertThrows on s.greatestCommonDivisor(0, 0)</t>
+  </si>
+  <si>
+    <t>line 32: assertThrows on s.intToMiniRoman(0); line 33: assertThrows on s.intToMiniRoman(1001)</t>
+  </si>
+  <si>
+    <t>line 23: expected 64 for doAlgebra(["**", "**"], [2, 3, 2]) but got 512; line 30: assertThrows on s.doAlgebra(List.of(), List.of(1))</t>
+  </si>
+  <si>
+    <t>line 37: assertThrows on s.findZero(List.of(1.0, 0.0, 1.0)); line 38: assertThrows on s.findZero(List.of(0.0, 0.0, 0.0))</t>
+  </si>
+  <si>
+    <t>line 24: assertThrows on s.changeBase(5, 1)</t>
+  </si>
+  <si>
+    <t>line 26: assertThrows on s.fib4(-1)</t>
+  </si>
+  <si>
+    <t>line 24: assertThrows on s.fib(0); line 25: assertThrows on s.fib(-1)</t>
+  </si>
+  <si>
+    <t>All suite results (gpt54 only)</t>
   </si>
 </sst>
 </file>
@@ -2858,7 +3141,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-m"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2912,7 +3195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2921,6 +3204,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3135,277 +3419,2265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA593DA-B4E3-4349-9AE3-137E67A4A1FB}">
+  <dimension ref="A1:G128"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="106.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="213.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:6" ht="18">
+      <c r="A1" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="F1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18">
+      <c r="A2" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D2" s="7">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18">
+      <c r="A3" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D3" s="7">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18">
+      <c r="A4" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="7">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18">
+      <c r="A5" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="7">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18">
+      <c r="A6" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18">
+      <c r="A7" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" s="7">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="18">
+      <c r="A8" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="7">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="18">
+      <c r="A9" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D9" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18">
+      <c r="A10" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18">
+      <c r="A11" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D11" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18">
+      <c r="A12" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="D12" s="7">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="18">
+      <c r="A13" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D13" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18">
+      <c r="A14" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D14" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18">
+      <c r="A15" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D15" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18">
+      <c r="A16" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="D16" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18">
+      <c r="A17" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D17" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="18">
+      <c r="A18" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D18" s="7">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="18">
+      <c r="A19" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D19" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="18">
+      <c r="A20" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="18">
+      <c r="A21" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="18">
+      <c r="A22" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="18">
+      <c r="A23" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D23" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="18">
+      <c r="A24" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="18">
+      <c r="A25" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D25" s="7">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="18">
+      <c r="A26" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D26" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18">
+      <c r="A27" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18">
+      <c r="A28" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18">
+      <c r="A29" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D29" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18">
+      <c r="A30" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D30" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18">
+      <c r="A31" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="D31" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>524</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46138.591990740744</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>444</v>
+      </c>
+      <c r="B34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>445</v>
+      </c>
+      <c r="B35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>446</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>447</v>
+      </c>
+      <c r="B37">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>448</v>
+      </c>
+      <c r="B38">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>449</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>450</v>
+      </c>
+      <c r="B40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>451</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>452</v>
+      </c>
+      <c r="B44" t="s">
+        <v>453</v>
+      </c>
+      <c r="C44" t="s">
+        <v>454</v>
+      </c>
+      <c r="D44" t="s">
+        <v>450</v>
+      </c>
+      <c r="E44" t="s">
+        <v>451</v>
+      </c>
+      <c r="F44" t="s">
+        <v>455</v>
+      </c>
+      <c r="G44" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>457</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="G45" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>459</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G46" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>461</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G47" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>462</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G48" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>464</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>1.6E-2</v>
+      </c>
+      <c r="G49" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>466</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0.01</v>
+      </c>
+      <c r="G50" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>467</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>19.704000000000001</v>
+      </c>
+      <c r="G51" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>468</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G52" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>469</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="G53" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>452</v>
+      </c>
+      <c r="B56" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>457</v>
+      </c>
+      <c r="B57" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>459</v>
+      </c>
+      <c r="B58" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>461</v>
+      </c>
+      <c r="B59" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>462</v>
+      </c>
+      <c r="B60" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>464</v>
+      </c>
+      <c r="B61" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>466</v>
+      </c>
+      <c r="B62" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>467</v>
+      </c>
+      <c r="B63" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>468</v>
+      </c>
+      <c r="B64" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>469</v>
+      </c>
+      <c r="B65" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>452</v>
+      </c>
+      <c r="B68" t="s">
+        <v>470</v>
+      </c>
+      <c r="C68" t="s">
+        <v>453</v>
+      </c>
+      <c r="D68" t="s">
+        <v>454</v>
+      </c>
+      <c r="E68" t="s">
+        <v>450</v>
+      </c>
+      <c r="F68" t="s">
+        <v>451</v>
+      </c>
+      <c r="G68" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>471</v>
+      </c>
+      <c r="B69" t="s">
+        <v>472</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>473</v>
+      </c>
+      <c r="B70" t="s">
+        <v>472</v>
+      </c>
+      <c r="C70">
+        <v>4</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>457</v>
+      </c>
+      <c r="B71" t="s">
+        <v>474</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>475</v>
+      </c>
+      <c r="B72" t="s">
+        <v>472</v>
+      </c>
+      <c r="C72">
+        <v>4</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>476</v>
+      </c>
+      <c r="B73" t="s">
+        <v>472</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>477</v>
+      </c>
+      <c r="B74" t="s">
+        <v>472</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>478</v>
+      </c>
+      <c r="B75" t="s">
+        <v>472</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>479</v>
+      </c>
+      <c r="B76" t="s">
+        <v>472</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>480</v>
+      </c>
+      <c r="B77" t="s">
+        <v>472</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>481</v>
+      </c>
+      <c r="B78" t="s">
+        <v>472</v>
+      </c>
+      <c r="C78">
+        <v>12</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>459</v>
+      </c>
+      <c r="B79" t="s">
+        <v>474</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>482</v>
+      </c>
+      <c r="B80" t="s">
+        <v>472</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>461</v>
+      </c>
+      <c r="B81" t="s">
+        <v>474</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>483</v>
+      </c>
+      <c r="B82" t="s">
+        <v>472</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>484</v>
+      </c>
+      <c r="B83" t="s">
+        <v>472</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>485</v>
+      </c>
+      <c r="B84" t="s">
+        <v>472</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>486</v>
+      </c>
+      <c r="B85" t="s">
+        <v>472</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>487</v>
+      </c>
+      <c r="B86" t="s">
+        <v>472</v>
+      </c>
+      <c r="C86">
+        <v>10</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>462</v>
+      </c>
+      <c r="B87" t="s">
+        <v>474</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>488</v>
+      </c>
+      <c r="B88" t="s">
+        <v>472</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>489</v>
+      </c>
+      <c r="B89" t="s">
+        <v>472</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>490</v>
+      </c>
+      <c r="B90" t="s">
+        <v>472</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>464</v>
+      </c>
+      <c r="B91" t="s">
+        <v>474</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>491</v>
+      </c>
+      <c r="B92" t="s">
+        <v>472</v>
+      </c>
+      <c r="C92">
+        <v>5</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>492</v>
+      </c>
+      <c r="B93" t="s">
+        <v>472</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>493</v>
+      </c>
+      <c r="B94" t="s">
+        <v>472</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>494</v>
+      </c>
+      <c r="B95" t="s">
+        <v>472</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>495</v>
+      </c>
+      <c r="B96" t="s">
+        <v>472</v>
+      </c>
+      <c r="C96">
+        <v>4</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>496</v>
+      </c>
+      <c r="B97" t="s">
+        <v>472</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>497</v>
+      </c>
+      <c r="B98" t="s">
+        <v>472</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>498</v>
+      </c>
+      <c r="B99" t="s">
+        <v>472</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>499</v>
+      </c>
+      <c r="B100" t="s">
+        <v>472</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>500</v>
+      </c>
+      <c r="B101" t="s">
+        <v>472</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>501</v>
+      </c>
+      <c r="B102" t="s">
+        <v>472</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>466</v>
+      </c>
+      <c r="B103" t="s">
+        <v>474</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>502</v>
+      </c>
+      <c r="B104" t="s">
+        <v>472</v>
+      </c>
+      <c r="C104">
+        <v>4</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>503</v>
+      </c>
+      <c r="B105" t="s">
+        <v>472</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>504</v>
+      </c>
+      <c r="B106" t="s">
+        <v>472</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>467</v>
+      </c>
+      <c r="B107" t="s">
+        <v>474</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>19.704000000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>505</v>
+      </c>
+      <c r="B108" t="s">
+        <v>472</v>
+      </c>
+      <c r="C108">
+        <v>4</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>468</v>
+      </c>
+      <c r="B109" t="s">
+        <v>474</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>506</v>
+      </c>
+      <c r="B110" t="s">
+        <v>472</v>
+      </c>
+      <c r="C110">
+        <v>8</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>507</v>
+      </c>
+      <c r="B111" t="s">
+        <v>472</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>508</v>
+      </c>
+      <c r="B112" t="s">
+        <v>472</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>509</v>
+      </c>
+      <c r="B113" t="s">
+        <v>472</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>510</v>
+      </c>
+      <c r="B114" t="s">
+        <v>472</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>469</v>
+      </c>
+      <c r="B115" t="s">
+        <v>474</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>511</v>
+      </c>
+      <c r="B116" t="s">
+        <v>472</v>
+      </c>
+      <c r="C116">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H11" s="2">
-        <f>COUNTIF(H2:H10, "Yes")/COUNTA(H2:H10)</f>
-        <v>0.33333333333333331</v>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>512</v>
+      </c>
+      <c r="B117" t="s">
+        <v>472</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>513</v>
+      </c>
+      <c r="B118" t="s">
+        <v>472</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>514</v>
+      </c>
+      <c r="B119" t="s">
+        <v>472</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>515</v>
+      </c>
+      <c r="B120" t="s">
+        <v>472</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>516</v>
+      </c>
+      <c r="B121" t="s">
+        <v>472</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>517</v>
+      </c>
+      <c r="B122" t="s">
+        <v>472</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>518</v>
+      </c>
+      <c r="B123" t="s">
+        <v>472</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>519</v>
+      </c>
+      <c r="B124" t="s">
+        <v>472</v>
+      </c>
+      <c r="C124">
+        <v>6</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>520</v>
+      </c>
+      <c r="B125" t="s">
+        <v>472</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>521</v>
+      </c>
+      <c r="B126" t="s">
+        <v>472</v>
+      </c>
+      <c r="C126">
+        <v>5</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>522</v>
+      </c>
+      <c r="B127" t="s">
+        <v>472</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>523</v>
+      </c>
+      <c r="B128" t="s">
+        <v>472</v>
+      </c>
+      <c r="C128">
+        <v>5</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>6.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3414,247 +5686,133 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>45</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G11" s="2">
-        <f>COUNTIF(G2:G10, "Yes")/COUNTA(G2:G10)</f>
-        <v>0.33333333333333331</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E8" s="2">
+        <f>COUNTIF(E2:E7, "Yes")/COUNTA(E2:E7)</f>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -3663,303 +5821,247 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1">
-        <v>1</v>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>141</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="H12" s="2">
-        <f>COUNTIF(H2:H11,"Yes")/COUNTA(H2:H11)</f>
-        <v>0.2</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G11" s="2">
+        <f>COUNTIF(G2:G10, "Yes")/COUNTA(G2:G10)</f>
+        <v>0.33333333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -3968,224 +6070,303 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>154</v>
+      <c r="B2" s="1">
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="1" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>143</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>109</v>
+        <v>144</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>143</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="1" t="b">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>145</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>145</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
+        <v>146</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>145</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G10" s="2">
-        <f>COUNTIF(G2:G9, "Yes")/COUNTA(G2:G9)</f>
-        <v>0.375</v>
+      <c r="B11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <c r="H12" s="2">
+        <f>COUNTIF(H2:H11,"Yes")/COUNTA(H2:H11)</f>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -4194,460 +6375,224 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA593DA-B4E3-4349-9AE3-137E67A4A1FB}">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="3" max="3" width="12.33203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="F1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="D2" s="7">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="D3" s="7">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="D4" s="7">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D5" s="7">
-        <v>3</v>
-      </c>
-      <c r="F5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="D6" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="D7" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="D8" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="D9" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D11" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D12" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="D13" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="E1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="D16" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="D17" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="D18" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D19" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D23" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="D25" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="D26" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D27" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A28" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="D28" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="D29" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A30" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="D30" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="18" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="D31" s="7">
-        <v>5</v>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G10" s="2">
+        <f>COUNTIF(G2:G9, "Yes")/COUNTA(G2:G9)</f>
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
@@ -4661,9 +6606,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4680,7 +6625,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -4697,7 +6642,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -4714,7 +6659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -4731,7 +6676,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -4748,7 +6693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>163</v>
       </c>
@@ -4765,7 +6710,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -4782,7 +6727,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -4799,7 +6744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="E9" s="2">
         <f>COUNTIF(E2:E8, "Yes")/COUNTA(E2:E8)</f>
         <v>0.2857142857142857</v>
@@ -4816,9 +6761,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4832,7 +6777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -4846,7 +6791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -4860,7 +6805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -4874,7 +6819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -4888,7 +6833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -4902,7 +6847,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -4916,7 +6861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -4930,7 +6875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -4944,7 +6889,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -4958,7 +6903,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="D11" s="2">
         <f>COUNTIF(D2:D10, "Yes")/COUNTA(D2:D10)</f>
         <v>0.1111111111111111</v>
@@ -4975,9 +6920,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4997,7 +6942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -5014,7 +6959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -5034,7 +6979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -5054,7 +6999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -5074,7 +7019,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -5094,7 +7039,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -5114,7 +7059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -5134,7 +7079,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -5154,7 +7099,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -5174,7 +7119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -5194,7 +7139,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -5214,7 +7159,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -5234,7 +7179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
@@ -5254,7 +7199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -5268,7 +7213,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -5282,7 +7227,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -5296,7 +7241,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -5316,7 +7261,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -5336,7 +7281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -5356,7 +7301,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="F21" s="2">
         <f>COUNTIF(F2:F20, "Yes") / COUNTA(F2:F20)</f>
         <v>0.15789473684210525</v>
@@ -5373,9 +7318,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5389,7 +7334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -5403,7 +7348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -5417,7 +7362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -5431,7 +7376,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -5445,7 +7390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -5459,7 +7404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -5473,7 +7418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -5487,7 +7432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -5501,7 +7446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -5515,7 +7460,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="D11" s="2">
         <f>COUNTIF(D2:D10, "Yes")/COUNTA(D2:D10)</f>
         <v>0.22222222222222221</v>
@@ -5532,9 +7477,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5554,7 +7499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -5571,7 +7516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -5591,7 +7536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -5611,7 +7556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -5631,7 +7576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -5651,7 +7596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -5668,7 +7613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -5683,7 +7628,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -5700,7 +7645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -5718,7 +7663,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -5738,7 +7683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -5758,7 +7703,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -5775,7 +7720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -5795,7 +7740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="F15" s="2">
         <f>COUNTIF(F2:F14,"Yes")/COUNTA(F2:F14)</f>
         <v>0.38461538461538464</v>
@@ -5812,9 +7757,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5837,7 +7782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -5860,7 +7805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -5883,7 +7828,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -5906,7 +7851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -5929,7 +7874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -5952,7 +7897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -5975,7 +7920,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -5998,7 +7943,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -6021,7 +7966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -6044,7 +7989,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="G11" s="2">
         <f>COUNTIF(G2:G10, "Yes")/COUNTA(G2:G10)</f>
         <v>0.22222222222222221</v>
@@ -6056,257 +8001,277 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>31</v>
+      <c r="B2" s="1">
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="1">
-        <v>2</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F13" s="2">
-        <f>COUNTIF(F2:F12,"Yes")/COUNTA(F2:F12)</f>
-        <v>0.18181818181818182</v>
+        <v>17</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="H11" s="2">
+        <f>COUNTIF(H2:H10, "Yes")/COUNTA(H2:H10)</f>
+        <v>0.33333333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -6320,9 +8285,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6345,7 +8310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -6368,7 +8333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -6391,7 +8356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -6414,7 +8379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -6431,7 +8396,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -6448,7 +8413,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -6471,7 +8436,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="G8" s="2">
         <f>COUNTIF(G2:G7, "Yes")/COUNTA(G2:G7)</f>
         <v>0.5</v>
@@ -6488,9 +8453,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6510,7 +8475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -6530,7 +8495,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -6550,7 +8515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -6570,7 +8535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -6590,7 +8555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -6610,7 +8575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -6630,7 +8595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -6650,7 +8615,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
@@ -6670,7 +8635,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -6690,7 +8655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -6710,7 +8675,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="F12" s="2">
         <f>COUNTIF(F2:F11,"Yes")/COUNTA(F2:F11)</f>
         <v>0.7</v>
@@ -6727,9 +8692,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6749,7 +8714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -6769,7 +8734,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -6789,7 +8754,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -6809,7 +8774,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -6829,7 +8794,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -6849,7 +8814,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -6869,7 +8834,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -6889,7 +8854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -6909,7 +8874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -6929,7 +8894,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="F11" s="2">
         <f>COUNTIF(F2:F10, "Yes")/COUNTA(F2:F10)</f>
         <v>0.44444444444444442</v>
@@ -6946,9 +8911,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6968,7 +8933,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -6988,7 +8953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -7008,7 +8973,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -7028,7 +8993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -7048,7 +9013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -7068,7 +9033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -7088,7 +9053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -7108,7 +9073,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="F9" s="2">
         <f>COUNTIF(F2:F8,"Yes")/COUNTA(F2:F8)</f>
         <v>0.42857142857142855</v>
@@ -7125,9 +9090,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7144,7 +9109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -7161,7 +9126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -7178,7 +9143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -7195,7 +9160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -7212,7 +9177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
@@ -7229,7 +9194,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -7246,7 +9211,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -7263,7 +9228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -7280,7 +9245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="E10" s="2">
         <f>COUNTIF(E2:E9, "Yes")/COUNTA(E2:E9)</f>
         <v>0.5</v>
@@ -7297,9 +9262,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7319,7 +9284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -7333,7 +9298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -7353,7 +9318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -7367,7 +9332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -7387,7 +9352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -7401,7 +9366,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -7421,7 +9386,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -7435,7 +9400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -7452,7 +9417,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -7469,7 +9434,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -7486,7 +9451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -7500,7 +9465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -7514,7 +9479,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -7528,7 +9493,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -7548,7 +9513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -7568,7 +9533,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -7588,7 +9553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -7608,7 +9573,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
@@ -7628,7 +9593,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -7648,7 +9613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="F21" s="2">
         <f>COUNTIF(F2:F20, "Yes")/COUNTA(F2:F20)</f>
         <v>0.47368421052631576</v>
@@ -7665,9 +9630,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7690,7 +9655,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -7713,7 +9678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -7736,7 +9701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -7759,7 +9724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -7782,7 +9747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -7805,7 +9770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -7819,7 +9784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -7833,7 +9798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -7850,7 +9815,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -7864,7 +9829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -7878,7 +9843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="G12" s="2">
         <f>COUNTIF(G2:G11, "Yes")/COUNTA(G2:G11)</f>
         <v>0.4</v>
@@ -7895,9 +9860,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7914,7 +9879,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -7931,7 +9896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -7948,7 +9913,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -7965,7 +9930,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -7982,7 +9947,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -7999,7 +9964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -8016,7 +9981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -8030,7 +9995,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="E9" s="2">
         <f>COUNTIF(E2:E8, "Yes")/COUNTA(E2:E8)</f>
         <v>0.7142857142857143</v>
@@ -8047,9 +10012,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8072,7 +10037,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -8095,7 +10060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -8118,7 +10083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -8141,7 +10106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -8164,7 +10129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -8187,7 +10152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -8210,7 +10175,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -8233,7 +10198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -8256,7 +10221,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -8279,7 +10244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
@@ -8302,7 +10267,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -8316,7 +10281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="G13" s="2">
         <f>COUNTIF(G2:G12,"Yes")/COUNTA(G2:G12)</f>
         <v>0.72727272727272729</v>
@@ -8333,9 +10298,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8349,7 +10314,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -8363,7 +10328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -8377,7 +10342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -8391,7 +10356,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -8405,7 +10370,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -8419,7 +10384,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -8433,7 +10398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -8447,7 +10412,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -8461,7 +10426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -8475,7 +10440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -8489,7 +10454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -8503,7 +10468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -8517,7 +10482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -8531,7 +10496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -8545,7 +10510,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -8559,7 +10524,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -8573,7 +10538,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="D18" s="2">
         <f>COUNTIF(D2:D17,"Yes")/COUNTA(D2:D17)</f>
         <v>0.625</v>
@@ -8585,25 +10550,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -8612,127 +10577,230 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F8" s="2">
-        <f>COUNTIF(F2:F7, "Yes")/COUNTA(F2:F7)</f>
-        <v>0.33333333333333331</v>
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="F13" s="2">
+        <f>COUNTIF(F2:F12,"Yes")/COUNTA(F2:F12)</f>
+        <v>0.18181818181818182</v>
       </c>
     </row>
   </sheetData>
@@ -8746,9 +10814,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8765,7 +10833,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -8782,7 +10850,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -8799,7 +10867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -8816,7 +10884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -8833,7 +10901,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -8850,7 +10918,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -8867,7 +10935,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -8884,7 +10952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -8901,7 +10969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -8918,7 +10986,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -8935,7 +11003,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
@@ -8952,7 +11020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -8969,7 +11037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -8986,7 +11054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -9003,7 +11071,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
@@ -9020,7 +11088,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -9037,7 +11105,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="E18" s="2">
         <f>COUNTIF(E2:E17,"Yes")/COUNTA(E2:E17)</f>
         <v>0.125</v>
@@ -9054,9 +11122,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9073,7 +11141,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -9090,7 +11158,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -9107,7 +11175,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -9124,7 +11192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -9141,7 +11209,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -9158,7 +11226,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -9175,7 +11243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -9192,7 +11260,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -9209,7 +11277,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="E10" s="2">
         <f>COUNTIF(E2:E9, "Yes")/COUNTA(E2:E9)</f>
         <v>0.375</v>
@@ -9221,14 +11289,14 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9236,22 +11304,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -9262,151 +11327,116 @@
         <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G9" s="2">
-        <f>COUNTIF(G2:G8, "Yes")/COUNTA(G2:G8)</f>
-        <v>0.42857142857142855</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="F8" s="2">
+        <f>COUNTIF(F2:F7, "Yes")/COUNTA(F2:F7)</f>
+        <v>0.33333333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -9415,337 +11445,220 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>46</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>26</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>59</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>26</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="6:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F17" s="2">
-        <f>COUNTIF(F2:F16,"Yes")/COUNTA(F2:F16)</f>
-        <v>0.13333333333333333</v>
+        <v>61</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="G9" s="2">
+        <f>COUNTIF(G2:G8, "Yes")/COUNTA(G2:G8)</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="H9">
+        <f>COUNTIF(H2:H8,"Yes")/COUNTA(H2:H8)</f>
+        <v>0.8571428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -9754,113 +11667,337 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>65</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>62</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="F12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E7" s="2">
-        <f>COUNTIF(E2:E6, "Yes")/COUNTA(E2:E6)</f>
-        <v>0.6</v>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" ht="15.75" customHeight="1">
+      <c r="F17" s="2">
+        <f>COUNTIF(F2:F16,"Yes")/COUNTA(F2:F16)</f>
+        <v>0.13333333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -9869,14 +12006,14 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9884,301 +12021,98 @@
         <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>83</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G14" s="2">
-        <f>COUNTIF(G2:G13, "Yes")/COUNTA(G2:G13)</f>
-        <v>0.33333333333333331</v>
+      <c r="E6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1">
+      <c r="E7" s="2">
+        <f>COUNTIF(E2:E6, "Yes")/COUNTA(E2:E6)</f>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -10187,137 +12121,316 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>93</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="G11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F7" s="2">
-        <f>COUNTIF(F2:F6, "Yes")/COUNTA(F2:F6)</f>
-        <v>0.4</v>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
+      <c r="G14" s="2">
+        <f>COUNTIF(G2:G13, "Yes")/COUNTA(G2:G13)</f>
+        <v>0.33333333333333331</v>
       </c>
     </row>
   </sheetData>
@@ -10326,133 +12439,137 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>103</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>108</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E8" s="2">
-        <f>COUNTIF(E2:E7, "Yes")/COUNTA(E2:E7)</f>
-        <v>0.5</v>
+        <v>110</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1">
+      <c r="F7" s="2">
+        <f>COUNTIF(F2:F6, "Yes")/COUNTA(F2:F6)</f>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
